--- a/data/trending_integrated_20261019_09.xlsx
+++ b/data/trending_integrated_20261019_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1216000</v>
+        <v>9710</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'-4.40%</t>
+          <t>'+14.91%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.03</v>
+        <v>0.16</v>
       </c>
       <c r="E2" t="n">
-        <v>800</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
-        <v>563</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>1711</v>
+        <v>98</v>
       </c>
       <c r="H2" t="n">
-        <v>48.82</v>
+        <v>6.15</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1272000</v>
+        <v>8450</v>
       </c>
       <c r="K2" t="n">
-        <v>1212000</v>
+        <v>9600</v>
       </c>
       <c r="L2" t="n">
-        <v>1219000</v>
+        <v>9880</v>
       </c>
       <c r="M2" t="n">
-        <v>1208000</v>
+        <v>9430</v>
       </c>
       <c r="N2" t="n">
-        <v>48.85</v>
+        <v>5.99</v>
       </c>
       <c r="O2" t="n">
-        <v>268944541000</v>
+        <v>7402469285</v>
       </c>
       <c r="P2" t="n">
-        <v>2987000</v>
+        <v>14940</v>
       </c>
       <c r="Q2" t="n">
-        <v>465500</v>
+        <v>5390</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,27 +626,211 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>정치적 요인으로 인한 주가 하락 및 반대매매, 정부 정책 비판.</t>
+          <t>테슬라 로드스터 납품 기대감에 따른 급등 전망. 자사주 매입 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>['테슬라', '로드스터', '자사주']</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>009900</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>213000</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>'-1.16%</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E3" t="n">
+        <v>800</v>
+      </c>
+      <c r="F3" t="n">
+        <v>552</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1557</v>
+      </c>
+      <c r="H3" t="n">
+        <v>45.99</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>215500</v>
+      </c>
+      <c r="K3" t="n">
+        <v>207000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>214500</v>
+      </c>
+      <c r="M3" t="n">
+        <v>206500</v>
+      </c>
+      <c r="N3" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="O3" t="n">
+        <v>499927718750</v>
+      </c>
+      <c r="P3" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>94500</v>
+      </c>
+      <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>대통령 선거 결과에 따른 주가 하락 우려. 투자자들의 의견 분분.</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="X2" t="n">
+      <c r="X3" t="n">
         <v>12</v>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1247000</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>'-1.97%</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E4" t="n">
+        <v>800</v>
+      </c>
+      <c r="F4" t="n">
+        <v>554</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1506</v>
+      </c>
+      <c r="H4" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1272000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1212000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1264000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1208000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="O4" t="n">
+        <v>631262287500</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>465500</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>정치적 이슈와 연계된 주가 하락 및 투자 심리 악화. 일부에서는 적정가 논의.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>['정치', '주가 하락', '적정가']</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20261019_09.xlsx
+++ b/data/trending_integrated_20261019_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9710</v>
+        <v>9500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+14.91%</t>
+          <t>'+12.43%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.16</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H2" t="n">
         <v>6.15</v>
@@ -610,7 +610,7 @@
         <v>5.99</v>
       </c>
       <c r="O2" t="n">
-        <v>7402469285</v>
+        <v>11327794755</v>
       </c>
       <c r="P2" t="n">
         <v>14940</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>테슬라 로드스터 납품 기대감에 따른 급등 전망. 자사주 매입 및 공매도 관련 언급.</t>
+          <t>테슬라 로드스터 관련 수혜 기대감 및 실적 개선 전망. 공매도에 대한 언급과 함께 자사주 매입 가능성 제기.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>213000</v>
+        <v>214750</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'-1.16%</t>
+          <t>'-0.35%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -673,10 +673,10 @@
         <v>800</v>
       </c>
       <c r="F3" t="n">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="G3" t="n">
-        <v>1557</v>
+        <v>1440</v>
       </c>
       <c r="H3" t="n">
         <v>45.99</v>
@@ -693,7 +693,7 @@
         <v>207000</v>
       </c>
       <c r="L3" t="n">
-        <v>214500</v>
+        <v>216000</v>
       </c>
       <c r="M3" t="n">
         <v>206500</v>
@@ -702,7 +702,7 @@
         <v>45.98</v>
       </c>
       <c r="O3" t="n">
-        <v>499927718750</v>
+        <v>662096023000</v>
       </c>
       <c r="P3" t="n">
         <v>374500</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>대통령 선거 결과에 따른 주가 하락 우려. 투자자들의 의견 분분.</t>
+          <t>대통령 선거와 관련된 정치적 이슈로 인한 하락세 우려. 외국인 순매수세 유입에 대한 기대감 혼재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['정치', '외국인', '하락']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="G4" t="n">
-        <v>1506</v>
+        <v>1444</v>
       </c>
       <c r="H4" t="n">
         <v>48.82</v>
@@ -794,7 +794,7 @@
         <v>48.85</v>
       </c>
       <c r="O4" t="n">
-        <v>631262287500</v>
+        <v>839576957000</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 주가 하락 및 투자 심리 악화. 일부에서는 적정가 논의.</t>
+          <t>정치적 불확실성 및 정부 정책에 대한 부정적 전망. 개인 투자자들의 손실 우려와 함께 단기 반등 가능성에 대한 회의적 시각.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치', '주가 하락', '적정가']</t>
+          <t>['정치', '손실', '전망']</t>
         </is>
       </c>
       <c r="X4" t="n">

--- a/data/trending_integrated_20261019_09.xlsx
+++ b/data/trending_integrated_20261019_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9500</v>
+        <v>9640</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+12.43%</t>
+          <t>'+14.08%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.16</v>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G2" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="H2" t="n">
         <v>6.15</v>
@@ -610,7 +610,7 @@
         <v>5.99</v>
       </c>
       <c r="O2" t="n">
-        <v>11327794755</v>
+        <v>12873600880</v>
       </c>
       <c r="P2" t="n">
         <v>14940</v>
@@ -619,19 +619,19 @@
         <v>5390</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-198000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>테슬라 로드스터 관련 수혜 기대감 및 실적 개선 전망. 공매도에 대한 언급과 함께 자사주 매입 가능성 제기.</t>
+          <t>테슬라 로드스터 수혜주 언급. 자사주 매입 관련 논의. 일부 공매도 및 매도 관련 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>214750</v>
+        <v>213000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'-1.16%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -673,10 +673,10 @@
         <v>800</v>
       </c>
       <c r="F3" t="n">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="G3" t="n">
-        <v>1440</v>
+        <v>1363</v>
       </c>
       <c r="H3" t="n">
         <v>45.99</v>
@@ -702,7 +702,7 @@
         <v>45.98</v>
       </c>
       <c r="O3" t="n">
-        <v>662096023000</v>
+        <v>757266630500</v>
       </c>
       <c r="P3" t="n">
         <v>374500</v>
@@ -711,14 +711,14 @@
         <v>94500</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>912000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>대통령 선거와 관련된 정치적 이슈로 인한 하락세 우려. 외국인 순매수세 유입에 대한 기대감 혼재.</t>
+          <t>기술격차 관련 뉴스 언급. 외국인 현물 매수 규모 확인. 일부 정치적 발언 다수.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['정치', '외국인', '하락']</t>
+          <t>['기술격차', '외국인', '뉴스']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1247000</v>
+        <v>14350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-1.97%</t>
+          <t>'-2.58%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
-        <v>549</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>1444</v>
+        <v>61</v>
       </c>
       <c r="H4" t="n">
-        <v>48.82</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1272000</v>
+        <v>14730</v>
       </c>
       <c r="K4" t="n">
-        <v>1212000</v>
+        <v>14500</v>
       </c>
       <c r="L4" t="n">
-        <v>1264000</v>
+        <v>14600</v>
       </c>
       <c r="M4" t="n">
-        <v>1208000</v>
+        <v>14120</v>
       </c>
       <c r="N4" t="n">
-        <v>48.85</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>839576957000</v>
+        <v>7897299335</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q4" t="n">
-        <v>465500</v>
+        <v>3320</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>32000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치적 불확실성 및 정부 정책에 대한 부정적 전망. 개인 투자자들의 손실 우려와 함께 단기 반등 가능성에 대한 회의적 시각.</t>
+          <t>주가 조작 및 뱅크런 관련 의혹 제기. 민주당 정책 및 정치인 언급 다수. 수주 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['정치', '손실', '전망']</t>
+          <t>['주가 조작', '뱅크런', '수주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -831,6 +831,98 @@
         </is>
       </c>
       <c r="Z4" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1228000</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'-3.46%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E5" t="n">
+        <v>800</v>
+      </c>
+      <c r="F5" t="n">
+        <v>530</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1425</v>
+      </c>
+      <c r="H5" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1272000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1212000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1264000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1208000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="O5" t="n">
+        <v>995206231000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>465500</v>
+      </c>
+      <c r="R5" t="n">
+        <v>67000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>주가 하락 관련 부정적 언급 다수. 정부 정책 및 정치적 발언 혼재. 일부 적정가 및 예상 주가 언급.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['주가 하락', '정부 정책', '정치']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20261019_09.xlsx
+++ b/data/trending_integrated_20261019_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>명신산업</t>
+          <t>KBI동양철관</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9640</v>
+        <v>1748</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+14.08%</t>
+          <t>'+29.96%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.16</v>
+        <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F2" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="H2" t="n">
-        <v>6.15</v>
+        <v>0.83</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>8450</v>
+        <v>1345</v>
       </c>
       <c r="K2" t="n">
-        <v>9600</v>
+        <v>1432</v>
       </c>
       <c r="L2" t="n">
-        <v>9880</v>
+        <v>1748</v>
       </c>
       <c r="M2" t="n">
-        <v>9430</v>
+        <v>1386</v>
       </c>
       <c r="N2" t="n">
-        <v>5.99</v>
+        <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>12873600880</v>
+        <v>18929507756</v>
       </c>
       <c r="P2" t="n">
-        <v>14940</v>
+        <v>2970</v>
       </c>
       <c r="Q2" t="n">
-        <v>5390</v>
+        <v>890</v>
       </c>
       <c r="R2" t="n">
-        <v>-198000</v>
+        <v>-65000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>테슬라 로드스터 수혜주 언급. 자사주 매입 관련 논의. 일부 공매도 및 매도 관련 언급.</t>
+          <t>KBI동양철관, 스페이스X 로켓 발사대에 강관 950톤 공급. 외인과 국민연금의 매수세 유입 확인.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['테슬라', '로드스터', '자사주']</t>
+          <t>['스페이스X', '강관', '납품']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>009900</t>
+          <t>008970</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>명신산업</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>213000</v>
+        <v>9510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'-1.16%</t>
+          <t>'+12.54%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>800</v>
+        <v>61</v>
       </c>
       <c r="F3" t="n">
-        <v>538</v>
+        <v>48</v>
       </c>
       <c r="G3" t="n">
-        <v>1363</v>
+        <v>101</v>
       </c>
       <c r="H3" t="n">
-        <v>45.99</v>
+        <v>6.15</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,51 +687,51 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>215500</v>
+        <v>8450</v>
       </c>
       <c r="K3" t="n">
-        <v>207000</v>
+        <v>9600</v>
       </c>
       <c r="L3" t="n">
-        <v>216000</v>
+        <v>9880</v>
       </c>
       <c r="M3" t="n">
-        <v>206500</v>
+        <v>9430</v>
       </c>
       <c r="N3" t="n">
-        <v>45.98</v>
+        <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>757266630500</v>
+        <v>13791520365</v>
       </c>
       <c r="P3" t="n">
-        <v>374500</v>
+        <v>14940</v>
       </c>
       <c r="Q3" t="n">
-        <v>94500</v>
+        <v>5390</v>
       </c>
       <c r="R3" t="n">
-        <v>912000</v>
+        <v>-198000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>기술격차 관련 뉴스 언급. 외국인 현물 매수 규모 확인. 일부 정치적 발언 다수.</t>
+          <t>명신산업, 테슬라 로드스터 수혜주로 언급되며 전체 매출 70% 테슬라 납품 사실 부각. 공매도 및 자사주 매입 관련 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['기술격차', '외국인', '뉴스']</t>
+          <t>['테슬라', '로드스터', '납품']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>009900</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14350</v>
+        <v>9120</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-2.58%</t>
+          <t>'+1.22%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.08</v>
+        <v>1.02</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="H4" t="n">
-        <v>9.699999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14730</v>
+        <v>9010</v>
       </c>
       <c r="K4" t="n">
-        <v>14500</v>
+        <v>8810</v>
       </c>
       <c r="L4" t="n">
-        <v>14600</v>
+        <v>9500</v>
       </c>
       <c r="M4" t="n">
-        <v>14120</v>
+        <v>8510</v>
       </c>
       <c r="N4" t="n">
-        <v>9.779999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="O4" t="n">
-        <v>7897299335</v>
+        <v>68540888120</v>
       </c>
       <c r="P4" t="n">
-        <v>40350</v>
+        <v>9500</v>
       </c>
       <c r="Q4" t="n">
-        <v>3320</v>
+        <v>2270</v>
       </c>
       <c r="R4" t="n">
-        <v>32000</v>
+        <v>40000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>주가 조작 및 뱅크런 관련 의혹 제기. 민주당 정책 및 정치인 언급 다수. 수주 관련 부정적 언급.</t>
+          <t>HT로보틱스, 로봇주로서의 관심 증가 및 목표가에 대한 기대감 존재. 야간 선물 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['주가 조작', '뱅크런', '수주']</t>
+          <t>['로봇주', '목표가', '야간선물']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1228000</v>
+        <v>213500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-3.46%</t>
+          <t>'-0.93%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="G5" t="n">
-        <v>1425</v>
+        <v>1339</v>
       </c>
       <c r="H5" t="n">
-        <v>48.82</v>
+        <v>45.99</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1272000</v>
+        <v>215500</v>
       </c>
       <c r="K5" t="n">
-        <v>1212000</v>
+        <v>207000</v>
       </c>
       <c r="L5" t="n">
-        <v>1264000</v>
+        <v>216000</v>
       </c>
       <c r="M5" t="n">
-        <v>1208000</v>
+        <v>206500</v>
       </c>
       <c r="N5" t="n">
-        <v>48.85</v>
+        <v>45.98</v>
       </c>
       <c r="O5" t="n">
-        <v>995206231000</v>
+        <v>850959413000</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q5" t="n">
-        <v>465500</v>
+        <v>94500</v>
       </c>
       <c r="R5" t="n">
-        <v>67000</v>
+        <v>912000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>주가 하락 관련 부정적 언급 다수. 정부 정책 및 정치적 발언 혼재. 일부 적정가 및 예상 주가 언급.</t>
+          <t>삼성전자, CXMT와 기술격차 관련 시장 우려 과도하다는 분석. 정치적 이슈와 함께 개인 매도 의견도 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['주가 하락', '정부 정책', '정치']</t>
+          <t>['CXMT', '기술격차', '시장우려']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -923,6 +923,190 @@
         </is>
       </c>
       <c r="Z5" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>14300</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'-2.92%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E6" t="n">
+        <v>47</v>
+      </c>
+      <c r="F6" t="n">
+        <v>28</v>
+      </c>
+      <c r="G6" t="n">
+        <v>69</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>14730</v>
+      </c>
+      <c r="K6" t="n">
+        <v>14500</v>
+      </c>
+      <c r="L6" t="n">
+        <v>14600</v>
+      </c>
+      <c r="M6" t="n">
+        <v>14120</v>
+      </c>
+      <c r="N6" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="O6" t="n">
+        <v>8788414160</v>
+      </c>
+      <c r="P6" t="n">
+        <v>40350</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3320</v>
+      </c>
+      <c r="R6" t="n">
+        <v>32000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>대우건설, 주가 조작 및 뱅크런에 대한 의혹 제기. 외인 보유율 관리 및 수주 관련 부정적 언급.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['주가조작', '뱅크런', '외인보유율']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1222000</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-3.93%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E7" t="n">
+        <v>800</v>
+      </c>
+      <c r="F7" t="n">
+        <v>516</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1434</v>
+      </c>
+      <c r="H7" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1272000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1212000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1264000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1208000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1121984661000</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>465500</v>
+      </c>
+      <c r="R7" t="n">
+        <v>67000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>SK하이닉스, 정치적 이슈와 함께 하락세에 대한 부정적 전망 다수. 솔리다임 상장 및 연기금 손실 관련 언급.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['솔리다임', '정치적이슈', '하락전망']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20261019_09.xlsx
+++ b/data/trending_integrated_20261019_09.xlsx
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>146</v>
+        <v>197</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>18929507756</v>
+        <v>19248245068</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -619,23 +619,23 @@
         <v>890</v>
       </c>
       <c r="R2" t="n">
-        <v>-65000</v>
+        <v>821000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>KBI동양철관, 스페이스X 로켓 발사대에 강관 950톤 공급. 외인과 국민연금의 매수세 유입 확인.</t>
+          <t>KBI동양철관, 스페이스X 로켓 발사대에 강관 950톤 공급 계약 체결. 국민연금 및 외국인 매수세 유입.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스페이스X', '강관', '납품']</t>
+          <t>['스페이스X', '공급 계약', '외국인 매수']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9510</v>
+        <v>9530</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.54%</t>
+          <t>'+12.78%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>13791520365</v>
+        <v>14367997760</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -711,23 +711,23 @@
         <v>5390</v>
       </c>
       <c r="R3" t="n">
-        <v>-198000</v>
+        <v>-327000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>명신산업, 테슬라 로드스터 수혜주로 언급되며 전체 매출 70% 테슬라 납품 사실 부각. 공매도 및 자사주 매입 관련 언급.</t>
+          <t>명신산업, 테슬라 로드스터 수혜주로 언급되며 매출 70% 테슬라 납품. 자사주 매입 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['테슬라', '로드스터', '납품']</t>
+          <t>['테슬라 로드스터', '자사주 매입', '공매도']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9120</v>
+        <v>9110</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.22%</t>
+          <t>'+1.11%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H4" t="n">
         <v>1.74</v>
@@ -794,7 +794,7 @@
         <v>0.72</v>
       </c>
       <c r="O4" t="n">
-        <v>68540888120</v>
+        <v>72523384085</v>
       </c>
       <c r="P4" t="n">
         <v>9500</v>
@@ -803,23 +803,23 @@
         <v>2270</v>
       </c>
       <c r="R4" t="n">
-        <v>40000</v>
+        <v>-197000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>HT로보틱스, 로봇주로서의 관심 증가 및 목표가에 대한 기대감 존재. 야간 선물 급락 가능성 언급.</t>
+          <t>HT로보틱스, 로봇주로서의 잠재력 언급. 단기 과열 우려 및 주포 움직임 주시.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇주', '목표가', '야간선물']</t>
+          <t>['로봇주', '주포', '단기과열']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>213500</v>
+        <v>214500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.93%</t>
+          <t>'-0.46%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>525</v>
+        <v>510</v>
       </c>
       <c r="G5" t="n">
-        <v>1339</v>
+        <v>1317</v>
       </c>
       <c r="H5" t="n">
         <v>45.99</v>
@@ -886,7 +886,7 @@
         <v>45.98</v>
       </c>
       <c r="O5" t="n">
-        <v>850959413000</v>
+        <v>966868244750</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -895,14 +895,14 @@
         <v>94500</v>
       </c>
       <c r="R5" t="n">
-        <v>912000</v>
+        <v>1113000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>504000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼성전자, CXMT와 기술격차 관련 시장 우려 과도하다는 분석. 정치적 이슈와 함께 개인 매도 의견도 존재.</t>
+          <t>삼성전자, CXMT와 기술 격차 관련 시장 우려 과도하다는 뉴스 인용. 개인 매도 및 외국인 매수.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['CXMT', '기술격차', '시장우려']</t>
+          <t>['CXMT', '기술 격차', '외국인 매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14300</v>
+        <v>14550</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-2.92%</t>
+          <t>'-1.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
         <v>69</v>
@@ -978,7 +978,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>8788414160</v>
+        <v>11005841025</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -987,10 +987,10 @@
         <v>3320</v>
       </c>
       <c r="R6" t="n">
-        <v>32000</v>
+        <v>33000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1222000</v>
+        <v>1231000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-3.93%</t>
+          <t>'-3.22%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="G7" t="n">
-        <v>1434</v>
+        <v>1339</v>
       </c>
       <c r="H7" t="n">
         <v>48.82</v>
@@ -1070,7 +1070,7 @@
         <v>48.85</v>
       </c>
       <c r="O7" t="n">
-        <v>1121984661000</v>
+        <v>1251631445000</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1079,23 +1079,23 @@
         <v>465500</v>
       </c>
       <c r="R7" t="n">
-        <v>67000</v>
+        <v>73000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>87000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>SK하이닉스, 정치적 이슈와 함께 하락세에 대한 부정적 전망 다수. 솔리다임 상장 및 연기금 손실 관련 언급.</t>
+          <t>SK하이닉스, 정치적 이슈 및 실적 관련 부정적 언급 다수. 솔라이덱스 상장 철회 요구.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['솔리다임', '정치적이슈', '하락전망']</t>
+          <t>['정치적 이슈', '솔라이덱스', '실적']</t>
         </is>
       </c>
       <c r="X7" t="n">
